--- a/data/trans_camb/P15B_3_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P15B_3_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-12,24</t>
+          <t>-12,33</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>2,76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,54</t>
+          <t>-7,66</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-44,06; 9,39</t>
+          <t>-47,18; 10,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-45,83; 10,01</t>
+          <t>-46,62; 9,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-42,08; 13,68</t>
+          <t>-45,71; 13,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,73</t>
+          <t>0,0; 51,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 40,5</t>
+          <t>4,51; 39,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,97</t>
+          <t>0,0; 14,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 16,63</t>
+          <t>-20,53; 16,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 14,07</t>
+          <t>-21,63; 15,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 6,94</t>
+          <t>-31,99; 6,52</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-51,09%</t>
+          <t>-51,47%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-50,83%</t>
+          <t>-51,65%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-92,54; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-77,75; —</t>
+          <t>-80,99; inf</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-83,66; 308,28</t>
+          <t>-77,71; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,27</t>
+          <t>8,45</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,12</t>
+          <t>5,8</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>7,15</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 33,67</t>
+          <t>2,92; 34,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,66</t>
+          <t>0,0; 35,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,41</t>
+          <t>0,0; 26,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -913,27 +913,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,63</t>
+          <t>0,0; 22,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,52</t>
+          <t>0,0; 20,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 17,59</t>
+          <t>1,61; 21,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 20,42</t>
+          <t>2,39; 19,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 16,51</t>
+          <t>2,38; 18,29</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-44,14</t>
+          <t>-44,82</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,52</t>
+          <t>4,29</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-39,41</t>
+          <t>-39,75</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-65,38; -24,01</t>
+          <t>-65,13; -25,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-62,73; -14,53</t>
+          <t>-64,97; -15,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-64,44; -20,56</t>
+          <t>-63,82; -19,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,0</t>
+          <t>0,0; 18,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-58,45; -19,79</t>
+          <t>-58,68; -21,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-56,19; -13,9</t>
+          <t>-56,56; -14,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-60,45; -16,63</t>
+          <t>-58,64; -18,26</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-63,47%</t>
+          <t>-64,45%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-66,6%</t>
+          <t>-67,19%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,35; -44,27</t>
+          <t>-82,42; -45,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-81,05; -25,49</t>
+          <t>-80,74; -25,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-82,7; -36,51</t>
+          <t>-81,69; -32,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-83,01; -45,06</t>
+          <t>-82,03; -45,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,97; -26,35</t>
+          <t>-82,85; -30,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-84,45; -35,27</t>
+          <t>-83,27; -36,21</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-6,26</t>
+          <t>-7,93</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-16,31</t>
+          <t>-16,99</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-10,67</t>
+          <t>-11,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-27,85; 7,73</t>
+          <t>-25,53; 9,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-35,44; 1,3</t>
+          <t>-35,86; 2,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 10,92</t>
+          <t>-26,71; 11,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-40,97; 2,07</t>
+          <t>-38,14; 1,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-42,55; -0,43</t>
+          <t>-41,58; 0,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-39,46; 3,02</t>
+          <t>-37,67; 3,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-25,91; 1,96</t>
+          <t>-24,67; 2,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-31,07; -3,9</t>
+          <t>-31,79; -5,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-25,01; 2,46</t>
+          <t>-25,32; 2,65</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-18,77%</t>
+          <t>-23,8%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-54,24%</t>
+          <t>-56,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-33,27%</t>
+          <t>-36,76%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-57,15; 38,61</t>
+          <t>-57,58; 48,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-75,75; 13,87</t>
+          <t>-77,11; 20,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,86; 50,1</t>
+          <t>-58,85; 52,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-86,86; 25,25</t>
+          <t>-85,08; 32,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-92,1; 24,49</t>
+          <t>-91,72; 20,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-85,81; 35,51</t>
+          <t>-84,71; 43,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 9,91</t>
+          <t>-58,84; 10,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-76,54; -16,01</t>
+          <t>-77,23; -16,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-60,52; 11,21</t>
+          <t>-62,5; 12,99</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10,31</t>
+          <t>8,71</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,22</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7,44</t>
+          <t>6,43</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 39,51</t>
+          <t>-23,99; 41,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-46,94; 11,08</t>
+          <t>-47,85; 10,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 42,41</t>
+          <t>-29,61; 39,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 3,85</t>
+          <t>-25,7; 3,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 17,93</t>
+          <t>-13,81; 18,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 13,94</t>
+          <t>-16,7; 11,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 16,77</t>
+          <t>-16,66; 16,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 11,96</t>
+          <t>-20,33; 11,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 22,32</t>
+          <t>-11,86; 21,96</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,13; 417,89</t>
+          <t>-49,36; 434,93</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-87,1; 238,52</t>
+          <t>-87,9; 157,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-52,95; 494,77</t>
+          <t>-65,41; 393,76</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1667,34 +1667,34 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-91,19; —</t>
+          <t>-79,38; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-70,38; —</t>
+          <t>-73,55; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-53,28; 274,1</t>
+          <t>-58,05; 235,02</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-72,35; 196,73</t>
+          <t>-69,03; 174,48</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-39,66; 328,81</t>
+          <t>-47,42; 365,07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,34</t>
+          <t>0,0; 6,53</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,07</t>
+          <t>0,0; 5,24</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-8,76</t>
+          <t>-9,56</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,52</t>
+          <t>-2,76</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-7,31</t>
+          <t>-7,76</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-20,87; -2,09</t>
+          <t>-21,02; -0,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-27,55; -6,78</t>
+          <t>-27,73; -7,78</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-20,23; 2,33</t>
+          <t>-20,33; 1,37</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 1,39</t>
+          <t>-13,74; 1,11</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 4,11</t>
+          <t>-11,57; 3,76</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 4,12</t>
+          <t>-11,31; 3,71</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-15,66; -2,51</t>
+          <t>-15,29; -2,29</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-18,4; -4,82</t>
+          <t>-18,0; -4,48</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-14,24; -0,17</t>
+          <t>-14,38; -0,96</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-27,06%</t>
+          <t>-29,54%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-24,9%</t>
+          <t>-27,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-32,19%</t>
+          <t>-34,2%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-53,52; -7,77</t>
+          <t>-53,55; -2,75</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-71,14; -27,7</t>
+          <t>-70,08; -28,95</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-50,72; 11,94</t>
+          <t>-53,35; 6,1</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-81,27; 34,13</t>
+          <t>-80,15; 37,66</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-68,69; 82,98</t>
+          <t>-69,68; 67,8</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-64,45; 80,12</t>
+          <t>-68,39; 65,55</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-56,8; -12,92</t>
+          <t>-55,29; -11,13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-66,46; -25,68</t>
+          <t>-65,56; -22,92</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-52,05; -0,04</t>
+          <t>-52,7; -4,78</t>
         </is>
       </c>
     </row>
